--- a/multi_regression/results_n_10_m_100_d_100/figs_100/regression_result.xlsx
+++ b/multi_regression/results_n_10_m_100_d_100/figs_100/regression_result.xlsx
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.1019 $\pm$ 0.0072</t>
+          <t>0.1093 $\pm$ 0.0075</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.1019 $\pm$ 0.0072</t>
+          <t>0.1091 $\pm$ 0.0076</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.1019 $\pm$ 0.0072</t>
+          <t>0.1091 $\pm$ 0.0077</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.1019 $\pm$ 0.0072</t>
+          <t>0.1092 $\pm$ 0.0075</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7.0961 $\pm$ 2.6961</t>
+          <t>6.8424 $\pm$ 2.0230</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11.5964 $\pm$ 3.7022</t>
+          <t>11.1607 $\pm$ 4.1498</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.7497 $\pm$ 2.8708</t>
+          <t>9.5089 $\pm$ 3.2480</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.5348 $\pm$ 2.7982</t>
+          <t>7.9350 $\pm$ 2.2690</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29580.1178 $\pm$ 18298.9972</t>
+          <t>35802.4468 $\pm$ 31757.3908</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18137.7733 $\pm$ 12997.6980</t>
+          <t>26261.3237 $\pm$ 24091.0056</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25830.8483 $\pm$ 22503.5179</t>
+          <t>24214.7111 $\pm$ 17298.1147</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28384.2180 $\pm$ 20486.8635</t>
+          <t>21473.4263 $\pm$ 11294.3551</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33314.1449 $\pm$ 22326.2681</t>
+          <t>45349.5497 $\pm$ 38229.1396</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22766.4606 $\pm$ 16790.2194</t>
+          <t>16678.5998 $\pm$ 14291.5517</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29396.2758 $\pm$ 22434.6158</t>
+          <t>22117.8380 $\pm$ 15285.9284</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23563.1090 $\pm$ 20271.7650</t>
+          <t>49997.5473 $\pm$ 34967.7965</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23050.5255 $\pm$ 13901.7232</t>
+          <t>110.8089 $\pm$ 27.4989</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15764.8256 $\pm$ 11266.2075</t>
+          <t>217.6487 $\pm$ 13.1178</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19481.6029 $\pm$ 9357.5748</t>
+          <t>153.0258 $\pm$ 13.8489</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21672.2101 $\pm$ 13776.3988</t>
+          <t>133.7082 $\pm$ 19.6066</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20.8726 $\pm$ 4.1033</t>
+          <t>41800.8407 $\pm$ 21830.8411</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>30.5530 $\pm$ 3.7139</t>
+          <t>42657.7857 $\pm$ 19716.9324</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29.1542 $\pm$ 4.2324</t>
+          <t>40924.6252 $\pm$ 21568.9562</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.6983 $\pm$ 4.2906</t>
+          <t>54809.4611 $\pm$ 16425.6082</t>
         </is>
       </c>
     </row>

--- a/multi_regression/results_n_10_m_100_d_100/figs_100/regression_result.xlsx
+++ b/multi_regression/results_n_10_m_100_d_100/figs_100/regression_result.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.1091 $\pm$ 0.0076</t>
+          <t>0.0911 $\pm$ 0.0055</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11.1607 $\pm$ 4.1498</t>
+          <t>9.5564 $\pm$ 2.6371</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26261.3237 $\pm$ 24091.0056</t>
+          <t>10959.0617 $\pm$ 10205.1491</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16678.5998 $\pm$ 14291.5517</t>
+          <t>20068.8825 $\pm$ 14268.5569</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>217.6487 $\pm$ 13.1178</t>
+          <t>196.2814 $\pm$ 8.5790</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>42657.7857 $\pm$ 19716.9324</t>
+          <t>39732.4532 $\pm$ 13240.8286</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
